--- a/src/assets/worklog/02.Slurry.xlsx
+++ b/src/assets/worklog/02.Slurry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\data\templates\worklog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E6A7DA-1E85-47E3-AC93-3532816AAD77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3963AA01-012B-414E-AAA3-71F326C86E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="525" windowWidth="14595" windowHeight="13965" xr2:uid="{D79008F3-FFA4-4AF2-A7AA-04C7085C44F6}"/>
+    <workbookView xWindow="1590" yWindow="300" windowWidth="26040" windowHeight="15045" xr2:uid="{D79008F3-FFA4-4AF2-A7AA-04C7085C44F6}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
     <definedName name="pdMixer4StartTime1">원본!$K$48</definedName>
     <definedName name="pdMixer4Temp1">원본!$H$48</definedName>
     <definedName name="plant">원본!$G$9</definedName>
-    <definedName name="productionId">원본!$G$7</definedName>
+    <definedName name="projectId">원본!$G$7</definedName>
     <definedName name="remark">원본!$A$54</definedName>
     <definedName name="reviewer">원본!$K$5</definedName>
     <definedName name="safety">원본!$K$52</definedName>
@@ -868,17 +868,68 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -889,31 +940,58 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -922,22 +1000,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -958,85 +1024,19 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1384,17 +1384,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1406,374 +1406,374 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="13"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="30"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9" t="s">
+      <c r="B7" s="52"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9" t="s">
+      <c r="F7" s="52"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9" t="s">
+      <c r="B9" s="52"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9" t="s">
+      <c r="F9" s="52"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="52"/>
+      <c r="K9" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="8"/>
+      <c r="L9" s="40"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="13"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="30"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10" t="s">
+      <c r="B12" s="52"/>
+      <c r="C12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="9" t="s">
+      <c r="D12" s="51"/>
+      <c r="E12" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10" t="s">
+      <c r="F12" s="52"/>
+      <c r="G12" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="9" t="s">
+      <c r="H12" s="51"/>
+      <c r="I12" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="10" t="s">
+      <c r="J12" s="52"/>
+      <c r="K12" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="10"/>
+      <c r="L12" s="51"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
+      <c r="A13" s="52"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="51"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="40"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="42"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="16"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="44"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="56" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="L17" s="57"/>
+      <c r="L17" s="35"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="59"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="37"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="56"/>
-      <c r="L19" s="57"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="35"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="31"/>
+      <c r="C20" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="63"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="61"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="39"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="62" t="s">
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="63"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="59"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="37"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="13"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="30"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="22"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="60"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20" t="s">
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20" t="s">
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
@@ -1782,8 +1782,8 @@
       <c r="B25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
       <c r="E25" s="2" t="s">
         <v>13</v>
       </c>
@@ -1802,10 +1802,10 @@
       <c r="J25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="K25" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="L25" s="8"/>
+      <c r="L25" s="40"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
@@ -1814,8 +1814,8 @@
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
       <c r="E26" s="2">
         <v>1</v>
       </c>
@@ -1836,8 +1836,8 @@
       <c r="B27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
       <c r="E27" s="2">
         <v>2</v>
       </c>
@@ -1856,8 +1856,8 @@
         <v>4</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
       <c r="E28" s="2">
         <v>3</v>
       </c>
@@ -1872,60 +1872,60 @@
       <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="13"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="30"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="31" t="s">
+      <c r="B30" s="52"/>
+      <c r="C30" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="32"/>
-      <c r="E30" s="23" t="s">
+      <c r="D30" s="54"/>
+      <c r="E30" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="35" t="s">
+      <c r="F30" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="G30" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="H30" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10" t="s">
+      <c r="J30" s="51"/>
+      <c r="K30" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="L30" s="10"/>
+      <c r="L30" s="51"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
+      <c r="A31" s="52"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
       <c r="I31" s="4" t="s">
         <v>42</v>
       </c>
@@ -1940,8 +1940,8 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26"/>
+      <c r="A32" s="43"/>
+      <c r="B32" s="44"/>
       <c r="C32" s="1" t="s">
         <v>46</v>
       </c>
@@ -1958,8 +1958,8 @@
       <c r="L32" s="1"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="27"/>
-      <c r="B33" s="28"/>
+      <c r="A33" s="45"/>
+      <c r="B33" s="46"/>
       <c r="C33" s="1" t="s">
         <v>48</v>
       </c>
@@ -1976,8 +1976,8 @@
       <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="27"/>
-      <c r="B34" s="28"/>
+      <c r="A34" s="45"/>
+      <c r="B34" s="46"/>
       <c r="C34" s="1" t="s">
         <v>48</v>
       </c>
@@ -1994,8 +1994,8 @@
       <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="27"/>
-      <c r="B35" s="28"/>
+      <c r="A35" s="45"/>
+      <c r="B35" s="46"/>
       <c r="C35" s="1" t="s">
         <v>49</v>
       </c>
@@ -2012,8 +2012,8 @@
       <c r="L35" s="1"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="27"/>
-      <c r="B36" s="28"/>
+      <c r="A36" s="45"/>
+      <c r="B36" s="46"/>
       <c r="C36" s="1" t="s">
         <v>49</v>
       </c>
@@ -2030,8 +2030,8 @@
       <c r="L36" s="1"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="27"/>
-      <c r="B37" s="28"/>
+      <c r="A37" s="45"/>
+      <c r="B37" s="46"/>
       <c r="C37" s="1" t="s">
         <v>17</v>
       </c>
@@ -2048,12 +2048,12 @@
       <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="27"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="29" t="s">
+      <c r="A38" s="45"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="30"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2064,14 +2064,14 @@
       <c r="L38" s="1"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="29" t="s">
+      <c r="B39" s="40"/>
+      <c r="C39" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="30"/>
+      <c r="D39" s="42"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -2081,8 +2081,8 @@
       <c r="L39" s="1"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="25"/>
-      <c r="B40" s="26"/>
+      <c r="A40" s="43"/>
+      <c r="B40" s="44"/>
       <c r="C40" s="1" t="s">
         <v>17</v>
       </c>
@@ -2099,8 +2099,8 @@
       <c r="L40" s="1"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="27"/>
-      <c r="B41" s="28"/>
+      <c r="A41" s="45"/>
+      <c r="B41" s="46"/>
       <c r="C41" s="1" t="s">
         <v>17</v>
       </c>
@@ -2117,8 +2117,8 @@
       <c r="L41" s="1"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="27"/>
-      <c r="B42" s="28"/>
+      <c r="A42" s="45"/>
+      <c r="B42" s="46"/>
       <c r="C42" s="1" t="s">
         <v>17</v>
       </c>
@@ -2135,8 +2135,8 @@
       <c r="L42" s="1"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="27"/>
-      <c r="B43" s="28"/>
+      <c r="A43" s="45"/>
+      <c r="B43" s="46"/>
       <c r="C43" s="1" t="s">
         <v>17</v>
       </c>
@@ -2153,12 +2153,12 @@
       <c r="L43" s="1"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="29" t="s">
+      <c r="A44" s="47"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="D44" s="30"/>
+      <c r="D44" s="42"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2169,14 +2169,14 @@
       <c r="L44" s="1"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="29" t="s">
+      <c r="B45" s="40"/>
+      <c r="C45" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="30"/>
+      <c r="D45" s="42"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2187,12 +2187,12 @@
       <c r="L45" s="1"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8" t="s">
+      <c r="A46" s="40"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D46" s="8"/>
+      <c r="D46" s="40"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2203,14 +2203,14 @@
       <c r="L46" s="1"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="29" t="s">
+      <c r="B47" s="40"/>
+      <c r="C47" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="30"/>
+      <c r="D47" s="42"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2221,12 +2221,12 @@
       <c r="L47" s="1"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="25" t="s">
+      <c r="A48" s="40"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="26"/>
+      <c r="D48" s="44"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2237,213 +2237,283 @@
       <c r="L48" s="1"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
-      <c r="L49" s="13"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="30"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="20" t="s">
+      <c r="A50" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="20"/>
-      <c r="C50" s="55" t="s">
+      <c r="B50" s="31"/>
+      <c r="C50" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="D50" s="54"/>
-      <c r="E50" s="20" t="s">
+      <c r="D50" s="32"/>
+      <c r="E50" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="F50" s="20"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="20" t="s">
+      <c r="F50" s="31"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J50" s="20"/>
-      <c r="K50" s="55" t="s">
+      <c r="J50" s="31"/>
+      <c r="K50" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="L50" s="54"/>
+      <c r="L50" s="32"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="13"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="30"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="20" t="s">
+      <c r="A52" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="20"/>
-      <c r="C52" s="54" t="s">
+      <c r="B52" s="31"/>
+      <c r="C52" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="54"/>
-      <c r="E52" s="20" t="s">
+      <c r="D52" s="32"/>
+      <c r="E52" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="54" t="s">
+      <c r="F52" s="31"/>
+      <c r="G52" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H52" s="54"/>
-      <c r="I52" s="20" t="s">
+      <c r="H52" s="32"/>
+      <c r="I52" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="J52" s="20"/>
-      <c r="K52" s="54" t="s">
+      <c r="J52" s="31"/>
+      <c r="K52" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="L52" s="54"/>
+      <c r="L52" s="32"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
-      <c r="L53" s="13"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="30"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="45"/>
-      <c r="B54" s="46"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="46"/>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="46"/>
-      <c r="H54" s="46"/>
-      <c r="I54" s="46"/>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="47"/>
+      <c r="A54" s="19"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="21"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="48"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="49"/>
-      <c r="K55" s="49"/>
-      <c r="L55" s="50"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="23"/>
+      <c r="J55" s="23"/>
+      <c r="K55" s="23"/>
+      <c r="L55" s="24"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="48"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
-      <c r="F56" s="49"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="49"/>
-      <c r="J56" s="49"/>
-      <c r="K56" s="49"/>
-      <c r="L56" s="50"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="23"/>
+      <c r="L56" s="24"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="48"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="49"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="49"/>
-      <c r="I57" s="49"/>
-      <c r="J57" s="49"/>
-      <c r="K57" s="49"/>
-      <c r="L57" s="50"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="23"/>
+      <c r="J57" s="23"/>
+      <c r="K57" s="23"/>
+      <c r="L57" s="24"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="48"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
-      <c r="J58" s="49"/>
-      <c r="K58" s="49"/>
-      <c r="L58" s="50"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="23"/>
+      <c r="K58" s="23"/>
+      <c r="L58" s="24"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="48"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="49"/>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="49"/>
-      <c r="J59" s="49"/>
-      <c r="K59" s="49"/>
-      <c r="L59" s="50"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="23"/>
+      <c r="K59" s="23"/>
+      <c r="L59" s="24"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="51"/>
-      <c r="B60" s="52"/>
-      <c r="C60" s="52"/>
-      <c r="D60" s="52"/>
-      <c r="E60" s="52"/>
-      <c r="F60" s="52"/>
-      <c r="G60" s="52"/>
-      <c r="H60" s="52"/>
-      <c r="I60" s="52"/>
-      <c r="J60" s="52"/>
-      <c r="K60" s="52"/>
-      <c r="L60" s="53"/>
+      <c r="A60" s="25"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="A32:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A40:B44"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
     <mergeCell ref="K14:L16"/>
     <mergeCell ref="A54:L60"/>
     <mergeCell ref="A6:L6"/>
@@ -2468,86 +2538,16 @@
     <mergeCell ref="K19:L21"/>
     <mergeCell ref="A20:B21"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A40:B44"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="A32:B38"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A30:B31"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:I24"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/02.Slurry.xlsx
+++ b/src/assets/worklog/02.Slurry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3963AA01-012B-414E-AAA3-71F326C86E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9FAB57-4CAD-45D2-8514-C10A79E2EE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1590" yWindow="300" windowWidth="26040" windowHeight="15045" xr2:uid="{D79008F3-FFA4-4AF2-A7AA-04C7085C44F6}"/>
+    <workbookView xWindow="-13635" yWindow="375" windowWidth="25260" windowHeight="15135" xr2:uid="{D79008F3-FFA4-4AF2-A7AA-04C7085C44F6}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -846,7 +846,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -868,6 +868,33 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -880,10 +907,67 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -931,18 +1015,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -959,84 +1031,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1384,17 +1378,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1406,374 +1400,374 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="63"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="63"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="63"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="30"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="13"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="52" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="52"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="52" t="s">
+      <c r="F7" s="9"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="52"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="52"/>
-      <c r="B8" s="52"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="40"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="52"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="52" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="52"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="52" t="s">
+      <c r="F9" s="9"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="52"/>
-      <c r="K9" s="40" t="s">
+      <c r="J9" s="9"/>
+      <c r="K9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="40"/>
+      <c r="L9" s="8"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="30"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="13"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="51" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="52" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="52"/>
-      <c r="G12" s="51" t="s">
+      <c r="F12" s="9"/>
+      <c r="G12" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="H12" s="51"/>
-      <c r="I12" s="52" t="s">
+      <c r="H12" s="10"/>
+      <c r="I12" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="J12" s="52"/>
-      <c r="K12" s="51" t="s">
+      <c r="J12" s="9"/>
+      <c r="K12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="51"/>
+      <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="52"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="51"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="14"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="42"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="16"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="44"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="18"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="46"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="34" t="s">
+      <c r="A17" s="16"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="L17" s="35"/>
+      <c r="L17" s="59"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="37"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="61"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="35"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="42"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="40" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="39"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="44"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="31"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="61" t="s">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="37"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="46"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="30"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="13"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="60"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="22"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31" t="s">
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
@@ -1782,8 +1776,8 @@
       <c r="B25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
       <c r="E25" s="2" t="s">
         <v>13</v>
       </c>
@@ -1802,10 +1796,10 @@
       <c r="J25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="40" t="s">
+      <c r="K25" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L25" s="40"/>
+      <c r="L25" s="8"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
@@ -1814,8 +1808,8 @@
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
       <c r="E26" s="2">
         <v>1</v>
       </c>
@@ -1836,8 +1830,8 @@
       <c r="B27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
       <c r="E27" s="2">
         <v>2</v>
       </c>
@@ -1856,8 +1850,8 @@
         <v>4</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
       <c r="E28" s="2">
         <v>3</v>
       </c>
@@ -1872,60 +1866,60 @@
       <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="30"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="13"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="52" t="s">
+      <c r="A30" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="52"/>
-      <c r="C30" s="53" t="s">
+      <c r="B30" s="9"/>
+      <c r="C30" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="54"/>
-      <c r="E30" s="49" t="s">
+      <c r="D30" s="34"/>
+      <c r="E30" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="57" t="s">
+      <c r="F30" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="49" t="s">
+      <c r="G30" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="49" t="s">
+      <c r="H30" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="I30" s="51" t="s">
+      <c r="I30" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51" t="s">
+      <c r="J30" s="10"/>
+      <c r="K30" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="L30" s="51"/>
+      <c r="L30" s="10"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="52"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
       <c r="I31" s="4" t="s">
         <v>42</v>
       </c>
@@ -1940,8 +1934,8 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="43"/>
-      <c r="B32" s="44"/>
+      <c r="A32" s="27"/>
+      <c r="B32" s="28"/>
       <c r="C32" s="1" t="s">
         <v>46</v>
       </c>
@@ -1958,8 +1952,8 @@
       <c r="L32" s="1"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="45"/>
-      <c r="B33" s="46"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="30"/>
       <c r="C33" s="1" t="s">
         <v>48</v>
       </c>
@@ -1976,8 +1970,8 @@
       <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="45"/>
-      <c r="B34" s="46"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="30"/>
       <c r="C34" s="1" t="s">
         <v>48</v>
       </c>
@@ -1994,8 +1988,8 @@
       <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="45"/>
-      <c r="B35" s="46"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="30"/>
       <c r="C35" s="1" t="s">
         <v>49</v>
       </c>
@@ -2012,8 +2006,8 @@
       <c r="L35" s="1"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="45"/>
-      <c r="B36" s="46"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="30"/>
       <c r="C36" s="1" t="s">
         <v>49</v>
       </c>
@@ -2030,8 +2024,8 @@
       <c r="L36" s="1"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="45"/>
-      <c r="B37" s="46"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
       <c r="C37" s="1" t="s">
         <v>17</v>
       </c>
@@ -2048,12 +2042,12 @@
       <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="45"/>
-      <c r="B38" s="46"/>
-      <c r="C38" s="41" t="s">
+      <c r="A38" s="29"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="42"/>
+      <c r="D38" s="32"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2064,14 +2058,14 @@
       <c r="L38" s="1"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="40" t="s">
+      <c r="A39" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="40"/>
-      <c r="C39" s="41" t="s">
+      <c r="B39" s="8"/>
+      <c r="C39" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="42"/>
+      <c r="D39" s="32"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -2081,8 +2075,8 @@
       <c r="L39" s="1"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="43"/>
-      <c r="B40" s="44"/>
+      <c r="A40" s="27"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="1" t="s">
         <v>17</v>
       </c>
@@ -2099,8 +2093,8 @@
       <c r="L40" s="1"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="45"/>
-      <c r="B41" s="46"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="30"/>
       <c r="C41" s="1" t="s">
         <v>17</v>
       </c>
@@ -2117,8 +2111,8 @@
       <c r="L41" s="1"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="45"/>
-      <c r="B42" s="46"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="30"/>
       <c r="C42" s="1" t="s">
         <v>17</v>
       </c>
@@ -2135,8 +2129,8 @@
       <c r="L42" s="1"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="45"/>
-      <c r="B43" s="46"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="1" t="s">
         <v>17</v>
       </c>
@@ -2153,12 +2147,12 @@
       <c r="L43" s="1"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="47"/>
-      <c r="B44" s="48"/>
-      <c r="C44" s="41" t="s">
+      <c r="A44" s="39"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="D44" s="42"/>
+      <c r="D44" s="32"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -2169,14 +2163,14 @@
       <c r="L44" s="1"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="40" t="s">
+      <c r="A45" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="40"/>
-      <c r="C45" s="41" t="s">
+      <c r="B45" s="8"/>
+      <c r="C45" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="42"/>
+      <c r="D45" s="32"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2187,12 +2181,12 @@
       <c r="L45" s="1"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="40"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="40" t="s">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D46" s="40"/>
+      <c r="D46" s="8"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -2203,14 +2197,14 @@
       <c r="L46" s="1"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="40" t="s">
+      <c r="A47" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="40"/>
-      <c r="C47" s="41" t="s">
+      <c r="B47" s="8"/>
+      <c r="C47" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="42"/>
+      <c r="D47" s="32"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2221,12 +2215,12 @@
       <c r="L47" s="1"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="40"/>
-      <c r="B48" s="40"/>
-      <c r="C48" s="43" t="s">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="44"/>
+      <c r="D48" s="28"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2237,283 +2231,213 @@
       <c r="L48" s="1"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="30"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="13"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="31" t="s">
+      <c r="A50" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="31"/>
-      <c r="C50" s="33" t="s">
+      <c r="B50" s="20"/>
+      <c r="C50" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="D50" s="32"/>
-      <c r="E50" s="31" t="s">
+      <c r="D50" s="56"/>
+      <c r="E50" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F50" s="31"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="31" t="s">
+      <c r="F50" s="20"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="J50" s="31"/>
-      <c r="K50" s="33" t="s">
+      <c r="J50" s="20"/>
+      <c r="K50" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="L50" s="32"/>
+      <c r="L50" s="56"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="28" t="s">
+      <c r="A51" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="30"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="13"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="31" t="s">
+      <c r="A52" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="32" t="s">
+      <c r="B52" s="20"/>
+      <c r="C52" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="32"/>
-      <c r="E52" s="31" t="s">
+      <c r="D52" s="56"/>
+      <c r="E52" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="31"/>
-      <c r="G52" s="32" t="s">
+      <c r="F52" s="20"/>
+      <c r="G52" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="H52" s="32"/>
-      <c r="I52" s="31" t="s">
+      <c r="H52" s="56"/>
+      <c r="I52" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="J52" s="31"/>
-      <c r="K52" s="32" t="s">
+      <c r="J52" s="20"/>
+      <c r="K52" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="L52" s="32"/>
+      <c r="L52" s="56"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="28" t="s">
+      <c r="A53" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="29"/>
-      <c r="J53" s="29"/>
-      <c r="K53" s="29"/>
-      <c r="L53" s="30"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="13"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="19"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="21"/>
+      <c r="A54" s="47"/>
+      <c r="B54" s="48"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="48"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="48"/>
+      <c r="H54" s="48"/>
+      <c r="I54" s="48"/>
+      <c r="J54" s="48"/>
+      <c r="K54" s="48"/>
+      <c r="L54" s="49"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="22"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="23"/>
-      <c r="K55" s="23"/>
-      <c r="L55" s="24"/>
+      <c r="A55" s="50"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="51"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="51"/>
+      <c r="G55" s="51"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="51"/>
+      <c r="K55" s="51"/>
+      <c r="L55" s="52"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="22"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="23"/>
-      <c r="J56" s="23"/>
-      <c r="K56" s="23"/>
-      <c r="L56" s="24"/>
+      <c r="A56" s="50"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="51"/>
+      <c r="D56" s="51"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
+      <c r="G56" s="51"/>
+      <c r="H56" s="51"/>
+      <c r="I56" s="51"/>
+      <c r="J56" s="51"/>
+      <c r="K56" s="51"/>
+      <c r="L56" s="52"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="22"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="23"/>
-      <c r="J57" s="23"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="24"/>
+      <c r="A57" s="50"/>
+      <c r="B57" s="51"/>
+      <c r="C57" s="51"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="51"/>
+      <c r="H57" s="51"/>
+      <c r="I57" s="51"/>
+      <c r="J57" s="51"/>
+      <c r="K57" s="51"/>
+      <c r="L57" s="52"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="22"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23"/>
-      <c r="I58" s="23"/>
-      <c r="J58" s="23"/>
-      <c r="K58" s="23"/>
-      <c r="L58" s="24"/>
+      <c r="A58" s="50"/>
+      <c r="B58" s="51"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="51"/>
+      <c r="G58" s="51"/>
+      <c r="H58" s="51"/>
+      <c r="I58" s="51"/>
+      <c r="J58" s="51"/>
+      <c r="K58" s="51"/>
+      <c r="L58" s="52"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="22"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="23"/>
-      <c r="J59" s="23"/>
-      <c r="K59" s="23"/>
-      <c r="L59" s="24"/>
+      <c r="A59" s="50"/>
+      <c r="B59" s="51"/>
+      <c r="C59" s="51"/>
+      <c r="D59" s="51"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="51"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="51"/>
+      <c r="I59" s="51"/>
+      <c r="J59" s="51"/>
+      <c r="K59" s="51"/>
+      <c r="L59" s="52"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="25"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
-      <c r="H60" s="26"/>
-      <c r="I60" s="26"/>
-      <c r="J60" s="26"/>
-      <c r="K60" s="26"/>
-      <c r="L60" s="27"/>
+      <c r="A60" s="53"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:L8"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:I24"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="A32:B38"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A30:B31"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A40:B44"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
     <mergeCell ref="K14:L16"/>
     <mergeCell ref="A54:L60"/>
     <mergeCell ref="A6:L6"/>
@@ -2538,16 +2462,86 @@
     <mergeCell ref="K19:L21"/>
     <mergeCell ref="A20:B21"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A40:B44"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="A32:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:L8"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/worklog/02.Slurry.xlsx
+++ b/src/assets/worklog/02.Slurry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\eurocell-mes-be\src\assets\worklog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9FAB57-4CAD-45D2-8514-C10A79E2EE31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E368EE-FF8E-4AA6-BA9D-9FDBE16F185E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13635" yWindow="375" windowWidth="25260" windowHeight="15135" xr2:uid="{D79008F3-FFA4-4AF2-A7AA-04C7085C44F6}"/>
+    <workbookView xWindow="4545" yWindow="675" windowWidth="13245" windowHeight="14235" xr2:uid="{D79008F3-FFA4-4AF2-A7AA-04C7085C44F6}"/>
   </bookViews>
   <sheets>
     <sheet name="원본" sheetId="1" r:id="rId1"/>
@@ -868,17 +868,68 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -889,37 +940,52 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -928,22 +994,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -964,73 +1018,19 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1378,17 +1378,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
       <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1400,374 +1400,374 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="A2" s="61"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="A3" s="61"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="13"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="30"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="9" t="s">
+      <c r="F7" s="50"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="A8" s="50"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9" t="s">
+      <c r="B9" s="50"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9" t="s">
+      <c r="F9" s="50"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="50"/>
+      <c r="K9" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="8"/>
+      <c r="L9" s="38"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="A10" s="50"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="13"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="30"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="10" t="s">
+      <c r="B12" s="50"/>
+      <c r="C12" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="9" t="s">
+      <c r="D12" s="49"/>
+      <c r="E12" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10" t="s">
+      <c r="F12" s="50"/>
+      <c r="G12" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="9" t="s">
+      <c r="H12" s="49"/>
+      <c r="I12" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="10" t="s">
+      <c r="J12" s="50"/>
+      <c r="K12" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="10"/>
+      <c r="L12" s="49"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
+      <c r="A13" s="50"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="41"/>
-      <c r="L14" s="42"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="44"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="16"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="46"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="58" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="L17" s="59"/>
+      <c r="L17" s="35"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="61"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="37"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="42"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="31"/>
+      <c r="C20" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="44"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="16"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="23" t="s">
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="46"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="18"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="13"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="30"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="22"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="58"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20" t="s">
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20" t="s">
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
@@ -1776,8 +1776,8 @@
       <c r="B25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
       <c r="E25" s="2" t="s">
         <v>13</v>
       </c>
@@ -1796,10 +1796,10 @@
       <c r="J25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="K25" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="L25" s="8"/>
+      <c r="L25" s="38"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
@@ -1808,8 +1808,8 @@
       <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
       <c r="E26" s="2">
         <v>1</v>
       </c>
@@ -1830,8 +1830,8 @@
       <c r="B27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
       <c r="E27" s="2">
         <v>2</v>
       </c>
@@ -1850,8 +1850,8 @@
         <v>4</v>
       </c>
       <c r="B28" s="2"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
       <c r="E28" s="2">
         <v>3</v>
       </c>
@@ -1866,60 +1866,60 @@
       <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="13"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="30"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="33" t="s">
+      <c r="B30" s="50"/>
+      <c r="C30" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="34"/>
-      <c r="E30" s="25" t="s">
+      <c r="D30" s="52"/>
+      <c r="E30" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="37" t="s">
+      <c r="F30" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="25" t="s">
+      <c r="G30" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="25" t="s">
+      <c r="H30" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10" t="s">
+      <c r="J30" s="49"/>
+      <c r="K30" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="L30" s="10"/>
+      <c r="L30" s="49"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
+      <c r="A31" s="50"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
       <c r="I31" s="4" t="s">
         <v>42</v>
       </c>
@@ -1934,8 +1934,8 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="27"/>
-      <c r="B32" s="28"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="42"/>
       <c r="C32" s="1" t="s">
         <v>46</v>
       </c>
@@ -1952,8 +1952,8 @@
       <c r="L32" s="1"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="29"/>
-      <c r="B33" s="30"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="44"/>
       <c r="C33" s="1" t="s">
         <v>48</v>
       </c>
@@ -1964,14 +1964,18 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
+      <c r="I33" s="1">
+        <v>20</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1500</v>
+      </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="29"/>
-      <c r="B34" s="30"/>
+      <c r="A34" s="43"/>
+      <c r="B34" s="44"/>
       <c r="C34" s="1" t="s">
         <v>48</v>
       </c>
@@ -1982,14 +1986,18 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="I34" s="1">
+        <v>20</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1500</v>
+      </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="29"/>
-      <c r="B35" s="30"/>
+      <c r="A35" s="43"/>
+      <c r="B35" s="44"/>
       <c r="C35" s="1" t="s">
         <v>49</v>
       </c>
@@ -2000,14 +2008,18 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
+      <c r="I35" s="1">
+        <v>20</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1500</v>
+      </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="29"/>
-      <c r="B36" s="30"/>
+      <c r="A36" s="43"/>
+      <c r="B36" s="44"/>
       <c r="C36" s="1" t="s">
         <v>49</v>
       </c>
@@ -2018,14 +2030,18 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
+      <c r="I36" s="1">
+        <v>20</v>
+      </c>
+      <c r="J36" s="1">
+        <v>1500</v>
+      </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="29"/>
-      <c r="B37" s="30"/>
+      <c r="A37" s="43"/>
+      <c r="B37" s="44"/>
       <c r="C37" s="1" t="s">
         <v>17</v>
       </c>
@@ -2036,18 +2052,22 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
+      <c r="I37" s="1">
+        <v>20</v>
+      </c>
+      <c r="J37" s="1">
+        <v>1500</v>
+      </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="29"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="31" t="s">
+      <c r="A38" s="43"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="D38" s="32"/>
+      <c r="D38" s="40"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -2058,14 +2078,14 @@
       <c r="L38" s="1"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="31" t="s">
+      <c r="B39" s="38"/>
+      <c r="C39" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="32"/>
+      <c r="D39" s="40"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -2075,8 +2095,8 @@
       <c r="L39" s="1"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="27"/>
-      <c r="B40" s="28"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="42"/>
       <c r="C40" s="1" t="s">
         <v>17</v>
       </c>
@@ -2087,14 +2107,18 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
+      <c r="I40" s="1">
+        <v>20</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1500</v>
+      </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="29"/>
-      <c r="B41" s="30"/>
+      <c r="A41" s="43"/>
+      <c r="B41" s="44"/>
       <c r="C41" s="1" t="s">
         <v>17</v>
       </c>
@@ -2105,14 +2129,18 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
+      <c r="I41" s="1">
+        <v>20</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1500</v>
+      </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="29"/>
-      <c r="B42" s="30"/>
+      <c r="A42" s="43"/>
+      <c r="B42" s="44"/>
       <c r="C42" s="1" t="s">
         <v>17</v>
       </c>
@@ -2123,14 +2151,18 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
+      <c r="I42" s="1">
+        <v>20</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1500</v>
+      </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="29"/>
-      <c r="B43" s="30"/>
+      <c r="A43" s="43"/>
+      <c r="B43" s="44"/>
       <c r="C43" s="1" t="s">
         <v>17</v>
       </c>
@@ -2141,36 +2173,42 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
+      <c r="I43" s="1">
+        <v>20</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1500</v>
+      </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="39"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="31" t="s">
+      <c r="A44" s="45"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="D44" s="32"/>
+      <c r="D44" s="40"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
+      <c r="I44" s="1">
+        <v>20</v>
+      </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="31" t="s">
+      <c r="B45" s="38"/>
+      <c r="C45" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="32"/>
+      <c r="D45" s="40"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -2181,30 +2219,34 @@
       <c r="L45" s="1"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8" t="s">
+      <c r="A46" s="38"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="D46" s="8"/>
+      <c r="D46" s="38"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
+      <c r="I46" s="1">
+        <v>20</v>
+      </c>
+      <c r="J46" s="1">
+        <v>300</v>
+      </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="31" t="s">
+      <c r="B47" s="38"/>
+      <c r="C47" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="32"/>
+      <c r="D47" s="40"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -2215,12 +2257,12 @@
       <c r="L47" s="1"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="27" t="s">
+      <c r="A48" s="38"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="28"/>
+      <c r="D48" s="42"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -2231,213 +2273,283 @@
       <c r="L48" s="1"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
-      <c r="K49" s="12"/>
-      <c r="L49" s="13"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="30"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="20" t="s">
+      <c r="A50" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="20"/>
-      <c r="C50" s="57" t="s">
+      <c r="B50" s="31"/>
+      <c r="C50" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="D50" s="56"/>
-      <c r="E50" s="20" t="s">
+      <c r="D50" s="32"/>
+      <c r="E50" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="F50" s="20"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="20" t="s">
+      <c r="F50" s="31"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="J50" s="20"/>
-      <c r="K50" s="57" t="s">
+      <c r="J50" s="31"/>
+      <c r="K50" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="L50" s="56"/>
+      <c r="L50" s="32"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
-      <c r="L51" s="13"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="30"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="20" t="s">
+      <c r="A52" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="20"/>
-      <c r="C52" s="56" t="s">
+      <c r="B52" s="31"/>
+      <c r="C52" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="D52" s="56"/>
-      <c r="E52" s="20" t="s">
+      <c r="D52" s="32"/>
+      <c r="E52" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="56" t="s">
+      <c r="F52" s="31"/>
+      <c r="G52" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="H52" s="56"/>
-      <c r="I52" s="20" t="s">
+      <c r="H52" s="32"/>
+      <c r="I52" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="J52" s="20"/>
-      <c r="K52" s="56" t="s">
+      <c r="J52" s="31"/>
+      <c r="K52" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="L52" s="56"/>
+      <c r="L52" s="32"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
-      <c r="K53" s="12"/>
-      <c r="L53" s="13"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="30"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="47"/>
-      <c r="B54" s="48"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="48"/>
-      <c r="J54" s="48"/>
-      <c r="K54" s="48"/>
-      <c r="L54" s="49"/>
+      <c r="A54" s="19"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="21"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="50"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="51"/>
-      <c r="J55" s="51"/>
-      <c r="K55" s="51"/>
-      <c r="L55" s="52"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="23"/>
+      <c r="J55" s="23"/>
+      <c r="K55" s="23"/>
+      <c r="L55" s="24"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="50"/>
-      <c r="B56" s="51"/>
-      <c r="C56" s="51"/>
-      <c r="D56" s="51"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="51"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="51"/>
-      <c r="I56" s="51"/>
-      <c r="J56" s="51"/>
-      <c r="K56" s="51"/>
-      <c r="L56" s="52"/>
+      <c r="A56" s="22"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="23"/>
+      <c r="L56" s="24"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="50"/>
-      <c r="B57" s="51"/>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="51"/>
-      <c r="G57" s="51"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="51"/>
-      <c r="J57" s="51"/>
-      <c r="K57" s="51"/>
-      <c r="L57" s="52"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="23"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="23"/>
+      <c r="J57" s="23"/>
+      <c r="K57" s="23"/>
+      <c r="L57" s="24"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="50"/>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="51"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="51"/>
-      <c r="I58" s="51"/>
-      <c r="J58" s="51"/>
-      <c r="K58" s="51"/>
-      <c r="L58" s="52"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="23"/>
+      <c r="K58" s="23"/>
+      <c r="L58" s="24"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="50"/>
-      <c r="B59" s="51"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="51"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="51"/>
-      <c r="I59" s="51"/>
-      <c r="J59" s="51"/>
-      <c r="K59" s="51"/>
-      <c r="L59" s="52"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23"/>
+      <c r="H59" s="23"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="23"/>
+      <c r="K59" s="23"/>
+      <c r="L59" s="24"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="53"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="54"/>
-      <c r="H60" s="54"/>
-      <c r="I60" s="54"/>
-      <c r="J60" s="54"/>
-      <c r="K60" s="54"/>
-      <c r="L60" s="55"/>
+      <c r="A60" s="25"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="A1:I5"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:H13"/>
+    <mergeCell ref="I12:J13"/>
+    <mergeCell ref="K12:L13"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="A32:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A40:B44"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="C45:D45"/>
     <mergeCell ref="K14:L16"/>
     <mergeCell ref="A54:L60"/>
     <mergeCell ref="A6:L6"/>
@@ -2462,86 +2574,16 @@
     <mergeCell ref="K19:L21"/>
     <mergeCell ref="A20:B21"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="A40:B44"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="A32:B38"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A30:B31"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:I24"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:H13"/>
-    <mergeCell ref="I12:J13"/>
-    <mergeCell ref="K12:L13"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:F10"/>
-    <mergeCell ref="G9:H10"/>
-    <mergeCell ref="I9:J10"/>
-    <mergeCell ref="K9:L10"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A1:I5"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="L2:L4"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F8"/>
-    <mergeCell ref="G7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
